--- a/public/work-samples/distribution-waterfall-model.xlsx
+++ b/public/work-samples/distribution-waterfall-model.xlsx
@@ -1016,6 +1016,7 @@
     </row>
     <row r="42" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1320,6 +1321,7 @@
     </row>
     <row r="43" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1645,6 +1647,7 @@
     </row>
     <row r="48" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2650,6 +2653,7 @@
     </row>
     <row r="77" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2975,6 +2979,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="D10:E10"/>
   </mergeCells>

--- a/public/work-samples/distribution-waterfall-model.xlsx
+++ b/public/work-samples/distribution-waterfall-model.xlsx
@@ -1016,7 +1016,7 @@
     </row>
     <row r="42" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
+  <sheetProtection password="CC0B" sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="43" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
+  <sheetProtection password="CC0B" sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="48" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
+  <sheetProtection password="CC0B" sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="77" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
+  <sheetProtection password="CC0B" sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2979,7 +2979,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
+  <sheetProtection password="CC0B" sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="D10:E10"/>
   </mergeCells>
